--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,70 @@
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>GILES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>COSSIO</t>
   </si>
   <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>PALACIOS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>CHAPARRO</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMISADAY</t>
+  </si>
+  <si>
+    <t>ANGEL OSWALDO</t>
+  </si>
+  <si>
+    <t>ALEXIS GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
+    <t>MAYKA XIMENA</t>
   </si>
   <si>
     <t>DIEGO</t>
@@ -501,13 +555,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>55.88</v>
+        <v>58.82</v>
       </c>
       <c r="H2">
         <v>5.4</v>
@@ -667,16 +721,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H2">
+        <v>5.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -690,16 +747,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -713,16 +773,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>43.48</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -736,16 +799,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H5">
+        <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -759,16 +825,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>88</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -824,16 +893,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>55.88</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -850,16 +919,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>81.81999999999999</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -876,16 +945,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>78.26000000000001</v>
+        <v>43.48</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,7 +980,7 @@
         <v>89.47</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,7 +1006,7 @@
         <v>88</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -947,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -985,10 +1054,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1002,25 +1071,163 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920279</v>
+        <v>24330051920174</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>24330051920182</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920257</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>23330051920231</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920220</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920279</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -128,9 +122,6 @@
   </si>
   <si>
     <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
@@ -1016,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1048,16 +1039,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920308</v>
+        <v>24330051920174</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1071,16 +1062,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920174</v>
+        <v>24330051920182</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1094,22 +1085,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920182</v>
+        <v>24330051920266</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1117,16 +1108,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920266</v>
+        <v>24330051920257</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1140,22 +1131,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920257</v>
+        <v>23330051920231</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1163,70 +1154,47 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920231</v>
+        <v>24330051920220</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920220</v>
+        <v>24330051920279</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920279</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MOTA</t>
   </si>
   <si>
@@ -103,12 +97,6 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>PALACIOS</t>
   </si>
   <si>
@@ -122,12 +110,6 @@
   </si>
   <si>
     <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
   </si>
   <si>
     <t>ANGEL OSWALDO</t>
@@ -1007,7 +989,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,22 +1021,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920174</v>
+        <v>24330051920266</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1062,22 +1044,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920182</v>
+        <v>24330051920257</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1085,22 +1067,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920266</v>
+        <v>23330051920231</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1108,93 +1090,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920257</v>
+        <v>24330051920220</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920231</v>
+        <v>24330051920279</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920220</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920279</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Mat</t>
   </si>
@@ -82,19 +82,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>MOTA</t>
   </si>
   <si>
     <t>PAZ</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>GILES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>PALACIOS</t>
@@ -103,13 +115,19 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>CHAPARRO</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>FIGUEROA</t>
   </si>
   <si>
-    <t>CHAPARRO</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMISADAY</t>
   </si>
   <si>
     <t>ANGEL OSWALDO</t>
@@ -118,13 +136,13 @@
     <t>ALEXIS GABRIEL</t>
   </si>
   <si>
+    <t>MAYKA XIMENA</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>ALEXA YAMILET</t>
-  </si>
-  <si>
-    <t>MAYKA XIMENA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1021,22 +1039,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920266</v>
+        <v>24330051920174</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1044,22 +1062,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920257</v>
+        <v>24330051920182</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1067,22 +1085,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920231</v>
+        <v>24330051920266</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1090,47 +1108,93 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920220</v>
+        <v>24330051920257</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920279</v>
+        <v>24330051920220</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920279</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G6">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920231</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -82,12 +82,54 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>SOTO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CORTEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MAZA</t>
+  </si>
+  <si>
+    <t>PICHARDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>MOTA</t>
   </si>
   <si>
@@ -103,6 +145,48 @@
     <t>GILES</t>
   </si>
   <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>ZOPILLAXTLE</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>CHACON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>PORRAS</t>
+  </si>
+  <si>
     <t>VILLA</t>
   </si>
   <si>
@@ -112,9 +196,6 @@
     <t>PALACIOS</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>CHAPARRO</t>
   </si>
   <si>
@@ -122,6 +203,57 @@
   </si>
   <si>
     <t>FIGUEROA</t>
+  </si>
+  <si>
+    <t>SANDY CAMILA</t>
+  </si>
+  <si>
+    <t>AYLIN ABIGAIL</t>
+  </si>
+  <si>
+    <t>LUZ ARIANA</t>
+  </si>
+  <si>
+    <t>BETZY AYELEN</t>
+  </si>
+  <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>ANGEL ISMAEL</t>
+  </si>
+  <si>
+    <t>BRYAN</t>
+  </si>
+  <si>
+    <t>GABRIEL URYEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ALEYDA MONSERRAT</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JHOCELIN VALENTINA</t>
+  </si>
+  <si>
+    <t>KEVIN JESUS</t>
+  </si>
+  <si>
+    <t>JIMENA</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>HEIDI ABRIL</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
@@ -1007,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1039,16 +1171,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920174</v>
+        <v>24330051920213</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1057,21 +1189,21 @@
         <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920182</v>
+        <v>24330051920187</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1080,121 +1212,512 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920266</v>
+        <v>24330051920201</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920257</v>
+        <v>24330051920194</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920220</v>
+        <v>24330051920202</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920279</v>
+        <v>24330051920247</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
+        <v>24330051920239</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>24330051920274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920267</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920369</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920312</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920308</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920179</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D14" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920298</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" t="s">
+        <v>75</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920316</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920255</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920262</v>
+      </c>
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920174</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920182</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920266</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920257</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920220</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920279</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
         <v>23330051920231</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="B25" t="s">
         <v>41</v>
       </c>
-      <c r="E8" t="s">
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s">
         <v>9</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F25" t="s">
         <v>14</v>
       </c>
-      <c r="G8">
+      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -82,199 +82,82 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>ZENDEJAS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CORTEZ</t>
+    <t>FRANCO</t>
   </si>
   <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>VERA</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MAZA</t>
-  </si>
-  <si>
-    <t>PICHARDO</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>NIETO</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>ZOPILLAXTLE</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>PINO</t>
   </si>
   <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>CHACON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>PORRAS</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
     <t>CHAPARRO</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>FIGUEROA</t>
+    <t>JESUS DAMIAN</t>
   </si>
   <si>
     <t>SANDY CAMILA</t>
   </si>
   <si>
-    <t>AYLIN ABIGAIL</t>
-  </si>
-  <si>
-    <t>LUZ ARIANA</t>
-  </si>
-  <si>
-    <t>BETZY AYELEN</t>
-  </si>
-  <si>
     <t>EVAN LAEL</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
     <t>YARETZY NAOMI</t>
   </si>
   <si>
-    <t>ANGEL ISMAEL</t>
-  </si>
-  <si>
-    <t>BRYAN</t>
-  </si>
-  <si>
-    <t>GABRIEL URYEL</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>ALEYDA MONSERRAT</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JHOCELIN VALENTINA</t>
-  </si>
-  <si>
-    <t>KEVIN JESUS</t>
-  </si>
-  <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>HEIDI ABRIL</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMISADAY</t>
-  </si>
-  <si>
-    <t>ANGEL OSWALDO</t>
-  </si>
-  <si>
-    <t>ALEXIS GABRIEL</t>
-  </si>
-  <si>
     <t>MAYKA XIMENA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ALEXA YAMILET</t>
   </si>
 </sst>
 </file>
@@ -1016,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>76.47</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,16 +925,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>75.76000000000001</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1068,16 +951,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>43.48</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1094,16 +977,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>89.47</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1120,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1171,22 +1054,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920213</v>
+        <v>24330051920260</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -1194,16 +1077,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920187</v>
+        <v>24330051920213</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1212,21 +1095,21 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920201</v>
+        <v>24330051920202</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1235,489 +1118,144 @@
         <v>10</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920194</v>
+        <v>24330051920407</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920202</v>
+        <v>24330051920369</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920247</v>
+        <v>24330051920308</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920239</v>
+        <v>24330051920388</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920274</v>
+        <v>24330051920247</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920267</v>
+        <v>24330051920220</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920369</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920312</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920308</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920179</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920298</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920316</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920255</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920262</v>
-      </c>
-      <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920174</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920182</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920266</v>
-      </c>
-      <c r="B21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920257</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920220</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920279</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920231</v>
-      </c>
-      <c r="B25" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="53">
   <si>
     <t>Mat</t>
   </si>
@@ -82,79 +82,97 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ZENDEJAS</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>NIETO</t>
   </si>
   <si>
     <t>BRAVO</t>
   </si>
   <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>SANDOVAL</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>COSSIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>PINO</t>
-  </si>
-  <si>
     <t>CHAPARRO</t>
   </si>
   <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>JESUS DAMIAN</t>
   </si>
   <si>
     <t>SANDY CAMILA</t>
   </si>
   <si>
+    <t>YARETZY NAOMI</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JHON STEVE</t>
+  </si>
+  <si>
+    <t>YURANI</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
     <t>EVAN LAEL</t>
   </si>
   <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
-    <t>YARETZY NAOMI</t>
   </si>
   <si>
     <t>MAYKA XIMENA</t>
@@ -1022,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,16 +1072,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920260</v>
+        <v>24330051920407</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1077,39 +1095,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920213</v>
+        <v>24330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920202</v>
+        <v>24330051920213</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1123,22 +1141,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920407</v>
+        <v>24330051920247</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -1149,13 +1167,13 @@
         <v>24330051920369</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1169,39 +1187,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920308</v>
+        <v>23330051920238</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920388</v>
+        <v>24330051920181</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1215,22 +1233,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920247</v>
+        <v>24330051920388</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1238,24 +1256,70 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920220</v>
+        <v>24330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920220</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
         <v>11</v>
       </c>
-      <c r="G10">
+      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20241.xlsx
@@ -91,24 +91,24 @@
     <t>GUERRA</t>
   </si>
   <si>
+    <t>ZENDEJAS</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ZENDEJAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -121,27 +121,27 @@
     <t>BRAVO</t>
   </si>
   <si>
+    <t>SANDOVAL</t>
+  </si>
+  <si>
     <t>PINO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
+    <t>COSSIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>ALCANTARA</t>
   </si>
   <si>
     <t>LIBRADO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
-    <t>COSSIO</t>
-  </si>
-  <si>
     <t>CHAPARRO</t>
   </si>
   <si>
@@ -154,25 +154,25 @@
     <t>SANDY CAMILA</t>
   </si>
   <si>
+    <t>EVAN LAEL</t>
+  </si>
+  <si>
     <t>YARETZY NAOMI</t>
   </si>
   <si>
     <t>JESUS ENRIQUE</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JANNIHA YUVIETH</t>
+  </si>
+  <si>
     <t>JHON STEVE</t>
   </si>
   <si>
     <t>YURANI</t>
-  </si>
-  <si>
-    <t>JANNIHA YUVIETH</t>
-  </si>
-  <si>
-    <t>EVAN LAEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
   </si>
   <si>
     <t>MAYKA XIMENA</t>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920247</v>
+        <v>24330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
@@ -1156,7 +1156,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>3</v>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920369</v>
+        <v>24330051920247</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>35</v>
@@ -1179,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920238</v>
+        <v>24330051920369</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1199,10 +1199,10 @@
         <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920181</v>
+        <v>24330051920308</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1256,7 +1256,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920202</v>
+        <v>23330051920238</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1268,10 +1268,10 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920308</v>
+        <v>24330051920181</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
